--- a/Single_Table_Combined.xlsx
+++ b/Single_Table_Combined.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,231 +440,266 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>RecordType</t>
+          <t>Vessel</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Vessel</t>
+          <t>Counterparty</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Counterparty</t>
+          <t>Route</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Route</t>
+          <t>ETA Start</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ETA Start</t>
+          <t>ETA End</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ETA End</t>
+          <t>ETA Midpoint</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>ETA Midpoint</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Email Sent Date</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Vessel_Clean</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Email Sent Date</t>
+          <t>Is_OOS</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Is_Optional</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BRS</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fixture</t>
+          <t>BW BREEZE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gas Camelot</t>
+          <t>BW LPG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>AG</t>
-        </is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46095</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46086</v>
+        <v>46096</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>46087</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>46086.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>96</v>
+        <v>46095.5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>VIA CAPE. OOS MAGELLAN 16-17 MAR VIA PANAMA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>05-06 Mar AG @ $96 : Total / Gas Camelot (Mercuria)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:53</t>
-        </is>
+          <t>Bw Breeze</t>
+        </is>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Breeze or BW Magellan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BW BREEZE</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BW LPG</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46095</v>
+      </c>
       <c r="F3" s="2" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>46095.5</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>46096.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>via Cape / via Pan NB 12th</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>VIA CAPE. OOS MAGELLAN 16-17 MAR VIA PANAMA</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Bw Breeze Or Bw Magellan</t>
+        </is>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Magellan os</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BW Breeze or BW Magellan</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46097</v>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>46096.5</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>46097.5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Northbound Panama 12 March</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>via Cape / via Pan NB 12th</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Bw Magellan</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW TBN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BW Magellan os</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46095</v>
+      </c>
       <c r="F5" s="2" t="n">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>46097.5</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Northbound Panama 12 March</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Bw Tbn</t>
+        </is>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -675,168 +710,204 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW TBN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BW TBN</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46095</v>
+      </c>
       <c r="F6" s="2" t="n">
-        <v>46095</v>
+        <v>46101</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="H6" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Bw Tbn</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BW TBN</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46098</v>
+      </c>
       <c r="F7" s="2" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>46098.5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Helios</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46098.5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Continental</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>46098.5</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>CONTINENTAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>HELIOS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46098.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VIA CAPE POSS</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>Continental</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>46098.5</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>USG via Cape</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -847,125 +918,152 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Helios</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46098.5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>Continental</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>46098.5</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Continental</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CONTINENTAL</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HELIOS</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46098</v>
+      </c>
       <c r="F11" s="2" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="H11" s="2" t="n">
         <v>46098.5</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>USG via Cape</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>VIA CAPE POSS</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Continental</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Pacific Binzhou</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Continental</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46099</v>
+      </c>
       <c r="F12" s="2" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46099</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>46098.5</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>46099.5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>via Pan sub NB</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Pacific Binzhou</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -976,39 +1074,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Virgo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pacific Binzhou</t>
+          <t>Wanhua</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46103</v>
+      </c>
       <c r="F13" s="2" t="n">
-        <v>46099</v>
+        <v>46104</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46100</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>46099.5</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>46103.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>swap - take back end March</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>via Pan sub NB</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Gas Virgo</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1019,174 +1126,204 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Virgo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Wanhua</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46103.5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Gas Virgo</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Wanhua</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" s="2" t="n">
-        <v>46103</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>46103.5</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Virgo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Wanhua</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46103.5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>Gas Virgo</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Wanhua</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" s="2" t="n">
-        <v>46103</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>46103.5</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>swap - take back end March</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>BRS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Messina</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gas Virgo</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wanhua</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46104</v>
+      </c>
       <c r="F16" s="2" t="n">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46104</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>46103.5</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>46104.5</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>23-24 Mar USG @ $154 &amp; $80 HF: Exxon / BW Messina (BP)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:53</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Bw Messina</t>
+        </is>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRS</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fixture</t>
+          <t>Sinddar</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BW Messina</t>
+          <t>PDEC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Exxon</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>USG</t>
-        </is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>46104</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46104</v>
+        <v>46108</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>46104.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>154</v>
+        <v>46106</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ex Petrobras TC</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23-24 Mar USG @ $154 &amp; $80 HF: Exxon / BW Messina (BP)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:53</t>
-        </is>
+          <t>Sinddar</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1197,125 +1334,152 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sinndar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Petredec</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>Sinndar</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Petredec</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" s="2" t="n">
-        <v>46105</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>46107</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>46106</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sunny Bright</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sinddar</t>
+          <t>Eneos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PDEC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46106</v>
+      </c>
       <c r="F19" s="2" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>46106</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>46106.5</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tentative relet. ETA Balboa 15 March</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ex Petrobras TC</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Sunny Bright</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>SOBAEK EXPLORER</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunny Bright</t>
+          <t>TRAFIGURA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Eneos</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F20" s="2" t="n">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46107</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>46106.5</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>46108.5</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VIA PANAMA (PMAX)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tentative relet. ETA Balboa 15 March</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Sobaek Explorer</t>
+        </is>
+      </c>
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1326,39 +1490,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>GAS VELA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUNNY BRIGHT</t>
+          <t>SINOGAS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ENEOS</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F21" s="2" t="n">
-        <v>46106</v>
+        <v>46109</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="H21" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VIA CAPE</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>VIA PANAMA</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Gas Vela</t>
+        </is>
+      </c>
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1369,125 +1542,152 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>SUNNY BRIGHT</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GAS VELA</t>
+          <t>ENEOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SINOGAS</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46106</v>
+      </c>
       <c r="F22" s="2" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H22" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VIA PANAMA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>VIA CAPE</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Sunny Bright</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sobaek Explorer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SOBAEK EXPLORER</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TRAFIGURA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F23" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H23" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Relet. Old-Style Panamax</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>VIA PANAMA (PMAX)</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Sobaek Explorer</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Vela</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sobaek Explorer</t>
+          <t>Sinogas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Trafigura</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F24" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H24" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Relet. Old-Style Panamax</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Gas Vela</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1498,39 +1698,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Vela</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Sinogas</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46108.5</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>USG via Cape.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>Gas Vela</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Sinogas</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" s="2" t="n">
-        <v>46108</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>46108.5</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>USG via Cape.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1541,82 +1750,100 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sobaek Explorer</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gas Vela</t>
+          <t>Trafi</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sinogas</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F26" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H26" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Pmax; via Pan sub NB</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Sobaek Explorer</t>
+        </is>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Vela</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sobaek Explorer</t>
+          <t>Sinogas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Trafi</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F27" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H27" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Pmax; via Pan sub NB</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Gas Vela</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1627,39 +1854,48 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sobaek Explorer PMAX</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sobaek Explorer PMAX</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Trafigura</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>46108</v>
+      </c>
       <c r="F28" s="2" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="H28" s="2" t="n">
         <v>46108.5</v>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Sobaek Explorer</t>
+        </is>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1670,125 +1906,152 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sunny Bright</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gas Vela</t>
+          <t>Eneos</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sinogas</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46106</v>
+      </c>
       <c r="F29" s="2" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>46108.5</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Sunny Bright</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sunny Bright</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pertamina Gas Caspia</t>
+          <t>Eneos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SCG</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>46106</v>
+      </c>
       <c r="F30" s="2" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H30" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ex NWE</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Sunny Bright</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Pertamina Gas Caspia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunny Bright</t>
+          <t>SCG</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Eneos</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46106</v>
+      </c>
       <c r="F31" s="2" t="n">
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H31" s="2" t="n">
         <v>46109</v>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ex NWE</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Pertamina Gas Caspia</t>
+        </is>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1799,39 +2062,48 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Vela</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sunny Bright</t>
+          <t>Sinogas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Eneos</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>46109</v>
+      </c>
       <c r="F32" s="2" t="n">
-        <v>46106</v>
+        <v>46110</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>46109.5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Gas Vela</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1842,131 +2114,152 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fixture</t>
+          <t>Pacific Binzhou</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>ATC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46109.5</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>28-29 Mar USG @ $149 : ATC / Pacific Binzhou (Shell)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:53</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>Pacific Binzhou</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>ATC</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>USG</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>46109</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>46109.5</v>
-      </c>
-      <c r="I33" t="n">
-        <v>149</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>28-29 Mar USG @ $149 : ATC / Pacific Binzhou (Shell)</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:53</t>
-        </is>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Hannibal</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gas Vela</t>
+          <t>Petredec</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sinogas</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>46111</v>
+      </c>
       <c r="F34" s="2" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>46109.5</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>46111.5</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Tentative relet. USG via Cape</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Hannibal</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Umm Laqhab</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Navigare Gaia</t>
+          <t>Neptune</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>46111</v>
+      </c>
       <c r="F35" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H35" s="2" t="n">
         <v>46111.5</v>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>USG via Cape</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>if via Panama / Pref AG</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Umm Laqhab</t>
+        </is>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1977,125 +2270,152 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Navigare Gaia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46111.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>if via Panama / Pref AG</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
           <t>Navigare Gaia</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Shell</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" s="2" t="n">
-        <v>46111</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>46111.5</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>if via Panama / Pref AG</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Navigare Gaia</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Umm Laqhab</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Neptune</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>46111</v>
+      </c>
       <c r="F37" s="2" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H37" s="2" t="n">
         <v>46111.5</v>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>if via Panama / Pref AG</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>USG via Cape</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Navigare Gaia</t>
+        </is>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Trafi TBN (can be PMAX)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hannibal</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Petredec</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>46113</v>
+      </c>
       <c r="F38" s="2" t="n">
-        <v>46111</v>
+        <v>46114</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>46112</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>46111.5</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>46113.5</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Tentative relet. USG via Cape</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Trafi Tbn</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2106,39 +2426,48 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Umm Laqhab</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>Neptune</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46113.5</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
           <t>Umm Laqhab</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Neptune</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>46113.5</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2149,39 +2478,48 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Umm Laqhab</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Neptune</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46113.5</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>Umm Laqhab</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Neptune</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>46113.5</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2192,39 +2530,48 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Danube River</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trafi TBN (can be PMAX)</t>
+          <t>Swisschem</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Trafigura</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>46113</v>
+      </c>
       <c r="F41" s="2" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46114</v>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>46113.5</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>via Panama / USG only</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Danube River</t>
+        </is>
+      </c>
+      <c r="K41" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2235,82 +2582,100 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Danube River</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>Swisschem</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>via Panama / USG only</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
           <t>Danube River</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Swisschem</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="H42" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>via Panama / USG only</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Clipper Explorer</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Danube River</t>
+          <t>Trafigura</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Swisschem</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>46114</v>
+      </c>
       <c r="F43" s="2" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="H43" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>46114.5</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Relet. Expected open Chiba. Old-Style Panamax</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>via Panama / USG only</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Clipper Explorer</t>
+        </is>
+      </c>
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2321,168 +2686,204 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>HLS Citrine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HLS Citrine</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>46114</v>
+      </c>
       <c r="F44" s="2" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="H44" s="2" t="n">
         <v>46114.5</v>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Old-Style Panamax</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Old-Style Panamax</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Hls Citrine</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Clipper Explorer PMAX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Trafigura</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46114</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46114.5</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
           <t>Clipper Explorer</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Trafigura</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="2" t="n">
-        <v>46114</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="H45" s="2" t="n">
-        <v>46114.5</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Relet. Expected open Chiba. Old-Style Panamax</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Danube River</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Clipper Explorer PMAX</t>
+          <t>SwissChem</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Trafigura</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>46115</v>
+      </c>
       <c r="F46" s="2" t="n">
-        <v>46114</v>
+        <v>46116</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="H46" s="2" t="n">
-        <v>46114.5</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
+        <v>46115.5</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Relet. Expected open Korea</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Danube River</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>DANUBE RIVER</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>SWISSCHEM</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46115.5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>VIA PANAMA 48KT +</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>Danube River</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SwissChem</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="2" t="n">
-        <v>46115</v>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>46116</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>46115.5</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Relet. Expected open Korea</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2493,340 +2894,412 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>UMM LAQHAB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DANUBE RIVER</t>
+          <t>NEPTUNE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SWISSCHEM</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>46115</v>
+      </c>
       <c r="F48" s="2" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>46116</v>
-      </c>
-      <c r="H48" s="2" t="n">
         <v>46115.5</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>VIA CAPE</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>VIA PANAMA 48KT +</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Umm Laqhab</t>
+        </is>
+      </c>
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Sirocco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UMM LAQHAB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NEPTUNE</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46115</v>
+      </c>
       <c r="F49" s="2" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="H49" s="2" t="n">
-        <v>46115.5</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>VIA CAPE</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Bw Sirocco</t>
+        </is>
+      </c>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>KEDARNATH</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BW Sirocco</t>
+          <t>PETREDEC</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>STL</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>46115</v>
+      </c>
       <c r="F50" s="2" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46117</v>
-      </c>
-      <c r="H50" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>VIA PANAMA, NOT FIRM</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Kedarnath</t>
+        </is>
+      </c>
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Frigg</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KEDARNATH</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PETREDEC</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>46116</v>
+      </c>
       <c r="F51" s="2" t="n">
-        <v>46115</v>
+        <v>46117</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46117</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>46116</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>46116.5</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Expected open India. USG via Cape</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>VIA PANAMA, NOT FIRM</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Bw Frigg</t>
+        </is>
+      </c>
+      <c r="K51" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Sansovino</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BW Frigg</t>
+          <t>Neptune</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>46116</v>
+      </c>
       <c r="F52" s="2" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46117</v>
-      </c>
-      <c r="H52" s="2" t="n">
         <v>46116.5</v>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>via Pan sub NB</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Expected open India. USG via Cape</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Sansovino</t>
+        </is>
+      </c>
+      <c r="K52" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Kedarnath</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sansovino</t>
+          <t>Petredec</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Neptune</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>46116</v>
+      </c>
       <c r="F53" s="2" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46117</v>
       </c>
-      <c r="H53" s="2" t="n">
-        <v>46116.5</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>via Panama / ex DD</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>via Pan sub NB</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Kedarnath</t>
+        </is>
+      </c>
+      <c r="K53" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>CORFU GAS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kedarnath</t>
+          <t>ADMIC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Petredec</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F54" s="2" t="n">
-        <v>46116</v>
+        <v>46118</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H54" s="2" t="n">
-        <v>46117</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
+        <v>46117.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PANAMAX, VIA CAPE</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>via Panama / ex DD</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Corfu Gas</t>
+        </is>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Jia Yuan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CORFU GAS</t>
+          <t>Keegan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ADMIC</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F55" s="2" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H55" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Relet. USG via Cape</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>PANAMAX, VIA CAPE</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Jia Yuan</t>
+        </is>
+      </c>
+      <c r="K55" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2837,125 +3310,152 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Oriental King os</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jia Yuan</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Keegan</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F56" s="2" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H56" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Expected open China</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Relet. USG via Cape</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Oriental King</t>
+        </is>
+      </c>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Corfu Gas PMAX</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oriental King os</t>
+          <t>AGT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F57" s="2" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H57" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Expected open China</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Corfu Gas</t>
+        </is>
+      </c>
+      <c r="K57" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Lycaste Peace</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Corfu Gas PMAX</t>
+          <t>Astomos</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AGT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>46113</v>
+      </c>
       <c r="F58" s="2" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H58" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>if via Cape - ex DD</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Lycaste Peace</t>
+        </is>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2966,174 +3466,204 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Kedarnath</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lycaste Peace</t>
+          <t>PDEC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Astomos</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>46113</v>
+      </c>
       <c r="F59" s="2" t="n">
-        <v>46113</v>
+        <v>46122</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H59" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>if via Pan - ex DD</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>if via Cape - ex DD</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Kedarnath</t>
+        </is>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Corfu Gas PMAX</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kedarnath</t>
+          <t>AGT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PDEC</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F60" s="2" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H60" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>if via Pan - ex DD</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Corfu Gas</t>
+        </is>
+      </c>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>BRS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Aries</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Corfu Gas PMAX</t>
+          <t>BGN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AGT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F61" s="2" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H61" s="2" t="n">
         <v>46117.5</v>
       </c>
-      <c r="I61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>05-06 Apr USG @ $145 : BGN / Gas Aries (E1)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:53</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Gas Aries</t>
+        </is>
+      </c>
+      <c r="K61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BRS</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fixture</t>
+          <t>Helios TBN (OOS PMAX)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Gas Aries</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BGN</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>USG</t>
-        </is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>46115</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="H62" s="2" t="n">
-        <v>46117.5</v>
-      </c>
-      <c r="I62" t="n">
-        <v>145</v>
+        <v>46118.5</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>via Panama / Cape</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>05-06 Apr USG @ $145 : BGN / Gas Aries (E1)</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:53</t>
-        </is>
+          <t>Helios Tbn</t>
+        </is>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3144,39 +3674,48 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Ocean Gas</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Helios TBN (OOS PMAX)</t>
+          <t>SwissChemGas</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="F63" s="2" t="n">
-        <v>46115</v>
+        <v>46119</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H63" s="2" t="n">
         <v>46118.5</v>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>via Panama / Cape</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Ocean Gas</t>
+        </is>
+      </c>
+      <c r="K63" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3187,125 +3726,152 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Ocean Gas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
+          <t>SwissChemGas</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46118.5</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Ocean Gas</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SwissChemGas</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="G64" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="H64" s="2" t="n">
-        <v>46118.5</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K64" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Jia Yuan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ocean Gas</t>
+          <t>Keegan</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SwissChemGas</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="F65" s="2" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="H65" s="2" t="n">
         <v>46118.5</v>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>if West via Cape</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Jia Yuan</t>
+        </is>
+      </c>
+      <c r="K65" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Oriental King</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jia Yuan</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Keegan</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="F66" s="2" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>46119</v>
       </c>
-      <c r="H66" s="2" t="n">
-        <v>46118.5</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>if West via Cape</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Oriental King</t>
+        </is>
+      </c>
+      <c r="K66" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -3316,168 +3882,200 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Oriental King</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
+          <t>BW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>via Panama</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Oriental King</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="G67" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="H67" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>ORIENTAL KING</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>BW LPG</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>46120</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>VIA PANAMA, SUB DISPORTS, PROGRAMME</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
           <t>Oriental King</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" s="2" t="n">
-        <v>46118</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>via Panama</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Helios TBN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ORIENTAL KING</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BW LPG</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F69" s="2" t="n">
-        <v>46118</v>
+        <v>46122</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="H69" s="2" t="n">
-        <v>46119</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
+        <v>46119.5</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>via Panama / Cape</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>VIA PANAMA, SUB DISPORTS, PROGRAMME</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Helios Tbn</t>
+        </is>
+      </c>
+      <c r="K69" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Fearnleys</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Helios TBN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Helios TBN</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>46117</v>
+      </c>
       <c r="F70" s="2" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H70" s="2" t="n">
         <v>46119.5</v>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:35</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>via Panama / Cape</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Helios Tbn</t>
+        </is>
+      </c>
+      <c r="K70" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3488,78 +4086,100 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Oriental King</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Helios TBN</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>46118</v>
+      </c>
       <c r="F71" s="2" t="n">
-        <v>46117</v>
+        <v>46122</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H71" s="2" t="n">
-        <v>46119.5</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
+        <v>46120</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>sub Pan</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
         <is>
           <t>2026-02-27 16:01:35</t>
         </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Oriental King</t>
+        </is>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fearnleys</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Cheyenne</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oriental King</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F72" s="2" t="n">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H72" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
+        <v>46120.5</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Expected open Indonesia. USG via Cape</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>sub Pan</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:35</t>
-        </is>
+          <t>Cheyenne</t>
+        </is>
+      </c>
+      <c r="K72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3570,39 +4190,48 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cheyenne</t>
+          <t>Wanhua</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F73" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="H73" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Relet. Expected open Turkey</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Expected open Indonesia. USG via Cape</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Al Ain</t>
+        </is>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3613,39 +4242,48 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Mindoro</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Wanhua</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>46119</v>
+      </c>
       <c r="F74" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="H74" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Expected open China</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Relet. Expected open Turkey</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Bw Mindoro</t>
+        </is>
+      </c>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3656,39 +4294,48 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Gas Neptune</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BW Mindoro</t>
+          <t>Sinogas</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F75" s="2" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H75" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Expected open Korea</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Expected open China</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Gas Neptune</t>
+        </is>
+      </c>
+      <c r="K75" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -3699,469 +4346,568 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW Tokyo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gas Neptune</t>
+          <t>BW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sinogas</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>46119</v>
+      </c>
       <c r="F76" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="H76" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Expected open Japan</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Expected open Korea</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Bw Tokyo</t>
+        </is>
+      </c>
+      <c r="K76" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>LAUREL PRIME</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BW Tokyo</t>
+          <t>ASTOMOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BW</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F77" s="2" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H77" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>VIA PANAMA. FACTORING 5 DAYS WAITING, MAERSK CODE</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Expected open Japan</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Laurel Prime</t>
+        </is>
+      </c>
+      <c r="K77" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LAUREL PRIME</t>
+          <t>Wanhua</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ASTOMOS</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F78" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="H78" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ex Med / 18-19 Mar ETA Yanbu via Suez</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>VIA PANAMA. FACTORING 5 DAYS WAITING, MAERSK CODE</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Al Ain</t>
+        </is>
+      </c>
+      <c r="K78" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Laurel Prime</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Astomos</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Wanhua</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F79" s="2" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="H79" s="2" t="n">
         <v>46120.5</v>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Relet. ETA Balboa 28 March</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ex Med / 18-19 Mar ETA Yanbu via Suez</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+          <t>Laurel Prime</t>
+        </is>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>GAS POWER</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Laurel Prime</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Astomos</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>46120</v>
+      </c>
       <c r="F80" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>46121</v>
       </c>
-      <c r="H80" s="2" t="n">
-        <v>46120.5</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>VIA PANAMA. POSS</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Relet. ETA Balboa 28 March</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Gas Power</t>
+        </is>
+      </c>
+      <c r="K80" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GAS POWER</t>
+          <t>Helios</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PTT</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>46121</v>
+      </c>
       <c r="F81" s="2" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H81" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="I81" t="inlineStr"/>
+        <v>46121.5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Expected open Indonesia. USG via Cape</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>VIA PANAMA. POSS</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Copernicus</t>
+        </is>
+      </c>
+      <c r="K81" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Badrinath</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Helios</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>46121</v>
+      </c>
       <c r="F82" s="2" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H82" s="2" t="n">
         <v>46121.5</v>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>via Cape/ Pref USG</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Expected open Indonesia. USG via Cape</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+          <t>Badrinath</t>
+        </is>
+      </c>
+      <c r="K82" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Poten</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Badrinath</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
+          <t>Exxon</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46121.5</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>USG via Cape</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:16</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
           <t>Badrinath</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Exxon</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="G83" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H83" s="2" t="n">
-        <v>46121.5</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>via Cape/ Pref USG</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+      <c r="K83" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Poten</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BADRINATH</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
+          <t>EXXON</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46121.5</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>PROGRAMMED?</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>Badrinath</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Exxon</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="G84" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H84" s="2" t="n">
-        <v>46121.5</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>USG via Cape</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:16</t>
-        </is>
+      <c r="K84" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Badrinath</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BADRINATH</t>
+          <t>Exxon</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>EXXON</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46121</v>
+      </c>
       <c r="F85" s="2" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H85" s="2" t="n">
         <v>46121.5</v>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>via Cape/ Pref USG</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>PROGRAMMED?</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Badrinath</t>
+        </is>
+      </c>
+      <c r="K85" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Affinity</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>GAS NEPTUNE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Badrinath</t>
+          <t>SINOGAS</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Exxon</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>46124</v>
+      </c>
       <c r="F86" s="2" t="n">
-        <v>46121</v>
+        <v>46127</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46122</v>
-      </c>
-      <c r="H86" s="2" t="n">
-        <v>46121.5</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
+        <v>46125.5</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>VIA PANAMA. NOT FIRM, SUB DISPORTS</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>via Cape/ Pref USG</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
+          <t>Gas Neptune</t>
+        </is>
+      </c>
+      <c r="K86" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -4172,82 +4918,100 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>BW LIBRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GAS NEPTUNE</t>
+          <t>BW LPG</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SINOGAS</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>46125</v>
+      </c>
       <c r="F87" s="2" t="n">
-        <v>46124</v>
+        <v>46127</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46127</v>
-      </c>
-      <c r="H87" s="2" t="n">
-        <v>46125.5</v>
-      </c>
-      <c r="I87" t="inlineStr"/>
+        <v>46126</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>VIA PANAMA. POSS</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:30</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>VIA PANAMA. NOT FIRM, SUB DISPORTS</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Bw Libra</t>
+        </is>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Affinity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Vishvakarmaa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BW LIBRA</t>
+          <t>SHV</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BW LPG</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>46126</v>
+      </c>
       <c r="F88" s="2" t="n">
-        <v>46125</v>
+        <v>46129</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46127</v>
-      </c>
-      <c r="H88" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="I88" t="inlineStr"/>
+        <v>46127.5</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:01:04</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>VIA PANAMA. POSS</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:30</t>
-        </is>
+          <t>Vishvakarmaa</t>
+        </is>
+      </c>
+      <c r="K88" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4258,82 +5022,48 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Vishvakarmaa</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>SHV</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>USG</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>46126</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>46129</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46127.5</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>via Cape</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-02-27 16:00:49</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>Vishvakarmaa</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>SHV</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="G89" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="H89" s="2" t="n">
-        <v>46127.5</v>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:01:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Affinity</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Vishvakarmaa</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>SHV</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" s="2" t="n">
-        <v>46126</v>
-      </c>
-      <c r="G90" s="2" t="n">
-        <v>46129</v>
-      </c>
-      <c r="H90" s="2" t="n">
-        <v>46127.5</v>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>via Cape</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>2026-02-27 16:00:49</t>
-        </is>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
